--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-dosis.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-dosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01</t>
+    <t>2026-09-02</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-dosis.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-dosis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>

--- a/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-dosis.xlsx
+++ b/branches/release/v2027.0.0-ballot.rc2/StructureDefinition-mii-pr-lungenfunktion-dosis.xlsx
@@ -982,6 +982,14 @@
     <t>sct</t>
   </si>
   <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://snomed.info/sct"/&gt;
+  &lt;version value="http://snomed.info/sct/900000000000207008/version/20250701"/&gt;
+  &lt;code value="1376040001"/&gt;
+  &lt;display value="Dose of methacholine to achieve maximal drop of forced expired volume in 1 second (observable entity)"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
     <t>Observation.code.coding:sct.id</t>
   </si>
   <si>
@@ -997,9 +1005,6 @@
     <t>Observation.code.coding:sct.code</t>
   </si>
   <si>
-    <t>1376040001</t>
-  </si>
-  <si>
     <t>Observation.code.coding:sct.display</t>
   </si>
   <si>
@@ -1012,6 +1017,13 @@
     <t>loinc</t>
   </si>
   <si>
+    <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
+  &lt;system value="http://loinc.org"/&gt;
+  &lt;code value="65866-6"/&gt;
+  &lt;display value="Methacholine [Mass] of Dose"/&gt;
+&lt;/valueCoding&gt;</t>
+  </si>
+  <si>
     <t>Observation.code.coding:loinc.id</t>
   </si>
   <si>
@@ -1025,9 +1037,6 @@
   </si>
   <si>
     <t>Observation.code.coding:loinc.code</t>
-  </si>
-  <si>
-    <t>65866-6</t>
   </si>
   <si>
     <t>Observation.code.coding:loinc.display</t>
@@ -6684,7 +6693,7 @@
         <v>81</v>
       </c>
       <c r="S39" t="s" s="2">
-        <v>81</v>
+        <v>310</v>
       </c>
       <c r="T39" t="s" s="2">
         <v>81</v>
@@ -6755,7 +6764,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>273</v>
@@ -6870,7 +6879,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>274</v>
@@ -6987,7 +6996,7 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>275</v>
@@ -7106,7 +7115,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>282</v>
@@ -7223,7 +7232,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>288</v>
@@ -7269,7 +7278,7 @@
         <v>81</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>315</v>
+        <v>81</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>81</v>
@@ -7626,7 +7635,7 @@
         <v>81</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>81</v>
+        <v>320</v>
       </c>
       <c r="T47" t="s" s="2">
         <v>81</v>
@@ -7697,7 +7706,7 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>273</v>
@@ -7812,7 +7821,7 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>274</v>
@@ -7929,7 +7938,7 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>275</v>
@@ -8048,7 +8057,7 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>282</v>
@@ -8165,7 +8174,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>288</v>
@@ -8211,7 +8220,7 @@
         <v>81</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>325</v>
+        <v>81</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>81</v>
